--- a/Desafio 4 - Vale Refeição/Desafio 4 - Dados/Base dias uteis - Informará o dia do PGTO e a Competência.xlsx
+++ b/Desafio 4 - Vale Refeição/Desafio 4 - Dados/Base dias uteis - Informará o dia do PGTO e a Competência.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thais.agne\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Cursos e Treinamentos\Cientista de Dados\Treinamento Python\I2A2\Desafios\Desafio 4 - Vale Refeição\Desafio 4 - Dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D178C1A7-CAA2-4A07-A0F3-5BCEDA11B60E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BDBE549-007D-46E7-BBE2-BAB9E13870C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{FEAC6BF2-C67E-44DA-A616-6A8EDEF16B11}"/>
+    <workbookView xWindow="9210" yWindow="2250" windowWidth="19140" windowHeight="13230" xr2:uid="{FEAC6BF2-C67E-44DA-A616-6A8EDEF16B11}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -27,16 +27,17 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>BASE DIAS UTEIS DE 15/04 a 15/05</t>
   </si>
@@ -50,20 +51,26 @@
     <t>SINDPD SP - SIND.TRAB.EM PROC DADOS E EMPR.EMPRESAS PROC DADOS ESTADO DE SP.</t>
   </si>
   <si>
-    <t>SINDPD RJ - SINDICATO PROFISSIONAIS DE PROC DADOS DO RIO DE JANEIRO</t>
-  </si>
-  <si>
     <t>SINDICADO</t>
   </si>
   <si>
     <t xml:space="preserve">DIAS UTEIS </t>
+  </si>
+  <si>
+    <t>ESTADO</t>
+  </si>
+  <si>
+    <t>RJ</t>
+  </si>
+  <si>
+    <t>SINDPD - SINDICATO PROFISSIONAIS DE PROC DADOS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -479,28 +486,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12D4A894-BE5F-4920-9800-4641A6D62D80}">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
-    <col min="2" max="2" width="17.1796875" customWidth="1"/>
+    <col min="2" max="2" width="17.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="15">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3">
       <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" ht="42.75">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -508,7 +518,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" ht="28.5">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -516,7 +526,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" ht="42.75">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -524,15 +534,18 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" ht="28.5">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B6" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="B7" s="3"/>
     </row>
   </sheetData>
